--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-LST-01_onayli_tedarikci_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-LST-01_onayli_tedarikci_listesi.xlsx
@@ -2403,7 +2403,8 @@
   <pageSetup paperSize="9" scale="24" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="1" differentOddEven="0" differentFirst="0" scaleWithDoc="0">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-LST-01&amp;C&amp;"Arial,Regular"&amp;11Onaylı Tedarikçi Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Tedarikçi performans başlıkları ortak yöntemle eşleştirildi; onay karar referansı ayrıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
